--- a/docs/all/01_TablasDescriptivas/idx12_salud_summary_labels.xlsx
+++ b/docs/all/01_TablasDescriptivas/idx12_salud_summary_labels.xlsx
@@ -460,7 +460,7 @@
         <v>125</v>
       </c>
       <c r="D4">
-        <v>-363.4762135039615</v>
+        <v>-363.4762135039616</v>
       </c>
       <c r="E4">
         <v>1248.59996013325</v>
